--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N92_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N92_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>62.71193827529704</v>
+        <v>10.19068996973577</v>
       </c>
       <c r="D2" t="n">
-        <v>23.67444830402453</v>
+        <v>3.847097849403987</v>
       </c>
       <c r="E2" t="n">
-        <v>19.17892295902312</v>
+        <v>3.116574980841257</v>
       </c>
       <c r="F2" t="n">
-        <v>3.567125157186271</v>
+        <v>0.5796578380427692</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.72213374159184</v>
+        <v>4.829846733008674</v>
       </c>
       <c r="D3" t="n">
-        <v>26.79206938471963</v>
+        <v>4.35371127501694</v>
       </c>
       <c r="E3" t="n">
-        <v>19.17892295902312</v>
+        <v>3.116574980841257</v>
       </c>
       <c r="F3" t="n">
-        <v>3.567125157186271</v>
+        <v>0.5796578380427692</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17.25163450893832</v>
+        <v>2.803390607702477</v>
       </c>
       <c r="D4" t="n">
-        <v>18.16430930504557</v>
+        <v>2.951700262069906</v>
       </c>
       <c r="E4" t="n">
-        <v>19.17892295902312</v>
+        <v>3.116574980841257</v>
       </c>
       <c r="F4" t="n">
-        <v>3.567125157186271</v>
+        <v>0.5796578380427692</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
